--- a/data_extactor/batch_10_fa/trimmed/batch_0015_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0015_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش | علوم پایه | راهبردهای یادگیری | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | علوم | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | محاسبات عددی | درک کتبی | درک شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>استدلال ریاضی | توانایی عددی | درک کتبی | درک شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | دانشمندان علوم داده | تحلیل‌گران کمی مسائل مالی | ریاضیدانان | تحلیل‌گران تحقیق در عملیات | تکنسین‌های آمار</t>
+          <t>کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | دانشمندان داده | تحلیل‌گران کمّی مالی | ریاضی‌دانان | تحلیل‌گران تحقیق در عملیات | دستیاران و تکنسین‌های آمار</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ریاضیات | علوم پایه | سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | شنیدن فعال | نگارش | راهبردهای یادگیری | نظارت</t>
+          <t>ریاضیات | علوم | سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | گوش دادن فعال | نگارش | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | استدلال استقرایی | درک کتبی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | محاسبات عددی</t>
+          <t>استدلال ریاضی | استدلال استقرایی | درک کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | توانایی عددی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دانشمندان بیوانفورماتیک | هماهنگ‌کنندگان کارآزمایی‌های بالینی | دانشمندان علوم داده | اپیدمیولوژیست‌ها | دانشمندان علوم پزشکی، به‌جز اپیدمیولوژیست‌ها | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار</t>
+          <t>متخصصان بیوانفورماتیک | هماهنگ‌کنندگان کارآزمایی‌های بالینی | دانشمندان داده | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | پژوهشگران و دانشمندان علوم پزشکی | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم پایه | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | مدیریت و امور اداری | اقتصاد و حسابداری</t>
+          <t>ریاضیات | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | تحلیل‌گران سیستم‌های رایانه‌ای | متخصصان انبارهای داده | معماران پایگاه داده | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار</t>
+          <t>تحلیل‌گران هوش تجاری | تحلیل‌گران سیستم‌های کامپیوتری | متخصصان انباره داده | معماران پایگاه داده | کارشناسان تحلیل مدیریت و روش‌ها | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری</t>
+          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تحلیل‌گران سیستم‌های رایانه‌ای | دانشمندان علوم داده | متخصصان انبارهای داده | معماران پایگاه داده | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | کارشناسان تحلیل بازار و بازاریابی | تحلیل‌گران تحقیق در عملیات</t>
+          <t>تحلیل‌گران سیستم‌های کامپیوتری | دانشمندان داده | متخصصان انباره داده | معماران پایگاه داده | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | تحلیل‌گران تحقیق در عملیات</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ریاضیات | پزشکی و دندان‌پزشکی</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی</t>
+          <t>استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان آمار زیستی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | مدیران پایگاه داده | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان مدارک و سوابق پزشکی | مدیران خدمات بهداشتی و درمانی</t>
+          <t>کارشناسان آمار زیستی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | مدیران پایگاه داده | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | مدیران خدمات درمانی و بهداشتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم پایه | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان محاسبات آماری و بیم‌سنجی (اکچوئری) | ریاضیدانان | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار | دانشمندان علوم داده | تحلیل‌گران کمی مسائل مالی | اقتصاددانان</t>
+          <t>اکچوئرها و کارشناسان محاسبات فنی بیمه | ریاضی‌دانان | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار | دانشمندان داده | تحلیل‌گران کمّی مالی | اقتصاددانان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | سخن گفتن | ریاضیات | نظارت | علوم پایه</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | سخن گفتن | ریاضیات | نظارت | علوم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات | استدلال ریاضی</t>
+          <t>درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دانشمندان بیوانفورماتیک | تکنسین‌های زیست‌شناسی | کارشناسان آمار زیستی | دانشمندان علوم داده | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان و تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | زیست‌شناسان سلولی و مولکولی</t>
+          <t>متخصصان بیوانفورماتیک | تکنسین‌های علوم زیستی | کارشناسان آمار زیستی | دانشمندان داده | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان علوم آزمایشگاهی بالینی | زیست‌شناسان سلولی و مولکولی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>طراحی | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مهندسی و فناوری | رایانه و الکترونیک | قوانین و مقررات | ریاضیات</t>
+          <t>طراحی | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مهندسی و فناوری | رایانه و الکترونیک | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تجسم فضایی | بیان شفاهی | بیان کتبی | ابتکار و اصالت | حساسیت به مسئله | استدلال قیاسی | درک کتبی</t>
+          <t>تجسم | بیان شفاهی | بیان کتبی | اصالت | حساسیت به مسئله | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نقشه‌کش‌های معماری و عمران | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز و ابنیه | بازرسان ساختمان و سازه | طراحان دکوراسیون و معماری داخلی | مهندسان معمار منظر</t>
+          <t>نقشه‌کشان معماری و عمران | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | طراحان داخلی | مهندسان معمار منظر</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | ابتکار و اصالت | تجسم فضایی | بیان کتبی | استدلال قیاسی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | اصالت | تجسم | بیان کتبی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کش‌های معماری و عمران | مهندسان عمران | مدیران ساخت‌وساز و ابنیه | سرپرستان کارگران فضای سبز، باغبانی و محوطه‌سازی | طراحان دکوراسیون و معماری داخلی | کارشناسان برنامه‌ریزی شهری و منطقه‌ای</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | طراحان داخلی | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | شنیدن فعال | یادگیری فعال | سخن گفتن | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | گوش دادن فعال | یادگیری فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک کتبی | دید نزدیک | درک شفاهی | استدلال استقرایی | استدلال قیاسی | مرتب‌سازی اطلاعات | تجسم فضایی</t>
+          <t>درک کتبی | بینایی نزدیک | درک شفاهی | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نقشه‌کش‌های معماری و عمران | نقشه‌برداران ژئودتیک | جغرافیدانان | تکنسین‌ها و متخصصان سیستم‌های اطلاعات جغرافیایی GIS | دانشمندان و متخصصان سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌بردار</t>
+          <t>نقشه‌کشان معماری و عمران | مهندسان نقشه‌برداری ژئودزی | جغرافیدانان | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | دانشمندان و فناوران سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌برداری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
